--- a/Python学习计划_四周.xlsx
+++ b/Python学习计划_四周.xlsx
@@ -15,12 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
   <si>
     <t xml:space="preserve">Python 四周学习计划表</t>
   </si>
   <si>
-    <t xml:space="preserve">每天 30 分钟（周一至周五 20:00-20:30）+ 周末 2 小时（09:00-11:00）｜共 28 天，4 周</t>
+    <t xml:space="preserve">工作日每天 30 分钟 + 周末每天 2 小时｜共 28 天，4 周</t>
   </si>
   <si>
     <t xml:space="preserve">周次</t>
@@ -29,9 +29,6 @@
     <t xml:space="preserve">星期</t>
   </si>
   <si>
-    <t xml:space="preserve">时间</t>
-  </si>
-  <si>
     <t xml:space="preserve">时长</t>
   </si>
   <si>
@@ -56,9 +53,6 @@
     <t xml:space="preserve">周一</t>
   </si>
   <si>
-    <t xml:space="preserve">20:00-20:30</t>
-  </si>
-  <si>
     <t xml:space="preserve">30分钟</t>
   </si>
   <si>
@@ -125,9 +119,6 @@
     <t xml:space="preserve">周六</t>
   </si>
   <si>
-    <t xml:space="preserve">09:00-11:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">2小时</t>
   </si>
   <si>
@@ -401,7 +392,7 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">1. 每天固定时段学习：工作日 20:00-20:30，周末 09:00-11:00，时间写入日历更不容易断。</t>
+    <t xml:space="preserve">1. 每天固定时段学习：工作日 30 分钟，周末 2 小时，时间写入日历更不容易断。</t>
   </si>
   <si>
     <t xml:space="preserve">2. “完成情况”列已做下拉选项（未开始 / 进行中 / 已完成），每天学完就更新一次。</t>
@@ -744,18 +735,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.5" customWidth="1"/>
     <col min="2" max="2" width="7.5" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="42" customWidth="1"/>
-    <col min="7" max="7" width="34" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="42" customWidth="1"/>
+    <col min="6" max="6" width="34" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -793,777 +783,690 @@
       <c r="H3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>12</v>
-      </c>
       <c r="C4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="F4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="13"/>
+      <c r="G4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="13"/>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="16" t="s">
+      <c r="F5" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="17"/>
+      <c r="G5" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="12" t="s">
+      <c r="F6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" s="13"/>
+      <c r="G6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="13"/>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="16" t="s">
+      <c r="F7" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="17"/>
+      <c r="G7" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="17"/>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="12" t="s">
+      <c r="F8" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="13"/>
+      <c r="G8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="13"/>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="E9" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="F9" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" s="17"/>
+      <c r="G9" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="17"/>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" s="13"/>
+      <c r="G10" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="13"/>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="H11" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="25"/>
+      <c r="G11" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="25"/>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>49</v>
+        <v>12</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>47</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="I12" s="21"/>
+        <v>48</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="21"/>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="22" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="24" t="s">
-        <v>52</v>
+        <v>12</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>50</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="H13" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13" s="25"/>
+        <v>51</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="25"/>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>55</v>
+        <v>12</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>53</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="H14" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" s="21"/>
+        <v>54</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="21"/>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="22" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="24" t="s">
-        <v>58</v>
+        <v>12</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>56</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="H15" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="I15" s="25"/>
+        <v>57</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="25"/>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>61</v>
+        <v>34</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>59</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="H16" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="21"/>
+        <v>60</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="21"/>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="22" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>42</v>
+        <v>34</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>61</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G17" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="H17" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="I17" s="25"/>
+        <v>62</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="25"/>
     </row>
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="F18" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="H18" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="I18" s="29"/>
+      <c r="G18" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="29"/>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="30" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="32" t="s">
-        <v>70</v>
+        <v>12</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>68</v>
       </c>
       <c r="F19" s="33" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="H19" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="I19" s="33"/>
+        <v>69</v>
+      </c>
+      <c r="G19" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="33"/>
     </row>
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="26" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="28" t="s">
-        <v>73</v>
+        <v>12</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>71</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="G20" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="H20" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="I20" s="29"/>
+        <v>72</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="29"/>
     </row>
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="30" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="32" t="s">
-        <v>76</v>
+        <v>12</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>74</v>
       </c>
       <c r="F21" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="G21" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="H21" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="I21" s="33"/>
+        <v>75</v>
+      </c>
+      <c r="G21" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="33"/>
     </row>
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="26" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="28" t="s">
-        <v>79</v>
+        <v>12</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="29" t="s">
+        <v>77</v>
       </c>
       <c r="F22" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="G22" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="H22" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="I22" s="29"/>
+        <v>78</v>
+      </c>
+      <c r="G22" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="29"/>
     </row>
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="30" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="E23" s="32" t="s">
-        <v>82</v>
+        <v>34</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" s="33" t="s">
+        <v>80</v>
       </c>
       <c r="F23" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="G23" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="H23" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="I23" s="33"/>
+        <v>81</v>
+      </c>
+      <c r="G23" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="33"/>
     </row>
     <row r="24" ht="34" customHeight="1">
       <c r="A24" s="26" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="D24" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E24" s="28" t="s">
-        <v>85</v>
+        <v>34</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="29" t="s">
+        <v>83</v>
       </c>
       <c r="F24" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="G24" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="H24" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="I24" s="29"/>
+        <v>84</v>
+      </c>
+      <c r="G24" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="29"/>
     </row>
     <row r="25" ht="34" customHeight="1">
       <c r="A25" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="F25" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="B25" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="F25" s="41" t="s">
-        <v>90</v>
-      </c>
-      <c r="G25" s="41" t="s">
-        <v>91</v>
-      </c>
-      <c r="H25" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="I25" s="41"/>
+      <c r="G25" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="41"/>
     </row>
     <row r="26" ht="34" customHeight="1">
       <c r="A26" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="E26" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="F26" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="B26" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="F26" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="G26" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="H26" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="I26" s="37"/>
+      <c r="G26" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="37"/>
     </row>
     <row r="27" ht="34" customHeight="1">
       <c r="A27" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="F27" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="B27" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="F27" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="G27" s="41" t="s">
-        <v>91</v>
-      </c>
-      <c r="H27" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="I27" s="41"/>
+      <c r="G27" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" s="41"/>
     </row>
     <row r="28" ht="34" customHeight="1">
       <c r="A28" s="34" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B28" s="35" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="36" t="s">
-        <v>96</v>
+        <v>12</v>
+      </c>
+      <c r="D28" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="E28" s="37" t="s">
+        <v>94</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="G28" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="H28" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="I28" s="37"/>
+        <v>95</v>
+      </c>
+      <c r="G28" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="37"/>
     </row>
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="38" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C29" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="40" t="s">
-        <v>99</v>
+        <v>12</v>
+      </c>
+      <c r="D29" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" s="41" t="s">
+        <v>97</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>100</v>
-      </c>
-      <c r="G29" s="41" t="s">
-        <v>101</v>
-      </c>
-      <c r="H29" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="I29" s="41"/>
+        <v>98</v>
+      </c>
+      <c r="G29" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="41"/>
     </row>
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="34" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B30" s="35" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="D30" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="E30" s="36" t="s">
-        <v>102</v>
+        <v>34</v>
+      </c>
+      <c r="D30" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="E30" s="37" t="s">
+        <v>100</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="G30" s="37" t="s">
-        <v>104</v>
-      </c>
-      <c r="H30" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="I30" s="37"/>
+        <v>101</v>
+      </c>
+      <c r="G30" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="37"/>
     </row>
     <row r="31" ht="34" customHeight="1">
       <c r="A31" s="38" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C31" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E31" s="40" t="s">
-        <v>105</v>
+        <v>34</v>
+      </c>
+      <c r="D31" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="E31" s="41" t="s">
+        <v>103</v>
       </c>
       <c r="F31" s="41" t="s">
-        <v>106</v>
-      </c>
-      <c r="G31" s="41" t="s">
-        <v>107</v>
-      </c>
-      <c r="H31" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="I31" s="41"/>
+        <v>104</v>
+      </c>
+      <c r="G31" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:A10"/>
     <mergeCell ref="A11:A17"/>
     <mergeCell ref="A18:A24"/>
     <mergeCell ref="A25:A31"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="输入有误" error="请从下拉列表中选择" sqref="H4:H31">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="输入有误" error="请从下拉列表中选择" sqref="G4:G31">
       <formula1>"⬜ 未开始,🟡 进行中,✅ 已完成"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1590,12 +1493,12 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
@@ -1603,99 +1506,99 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="46" t="s">
         <v>115</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="F4" s="47" t="s">
         <v>116</v>
-      </c>
-      <c r="D4" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="E4" s="46" t="s">
-        <v>118</v>
-      </c>
-      <c r="F4" s="47" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="48" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C5" s="50" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D5" s="51" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E5" s="52" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F5" s="53" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="42" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D6" s="45" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F6" s="47" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="48" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E7" s="52" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F7" s="53" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1718,52 +1621,52 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="51" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="54" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="54" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="54" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="54" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="54" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="54" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="54" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="54" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="54" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
